--- a/output_excel/16794910.xlsx
+++ b/output_excel/16794910.xlsx
@@ -564,18 +564,18 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>32m</t>
+          <t>14.81m</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>112,5KVA | C14X1000112,5KVACE4 | CE3 | 3x185AX(5AZN) | MT | V4-5 | CLANDESTINOS: | GUSMAO | LAURO | AV. | 32M | SILVEIRA | CE4 | C14X1000112,5KVACE2 | 112,5KVA112,5KVA400816F | LADO | V6-7 | 3x336AN | RAMAL | CE4112,5KVA | ANCORAR | 30K | P4-30</t>
+          <t>AV. | LAURO | 2</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NAO</t>
         </is>
       </c>
     </row>
@@ -612,11 +612,11 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>P5 | 512716 | 3x336AN | BF-A | 112,5KVA | 37,5KVA | 112,5KVA | EP | 112,5KVA | RUA | RUA | 112,5KVA | BF-A | (DCIM) | ANCORAR | 1x2x4AC | (DCIM) | CAMPO | (DCIM) | 30K | AVENIDA | 1x2x4AC | CABOS | (DCIM) | 112,5KVA | 112,5KVA | 3x336AN | LADO | 1AF(1) | LADO | 112,5KVA | 112,5KVA | BM | (DCIM) | (DCIM) | 112,5KVA112,5KVA | 112,5KVA112,5KVA | 112,5KVA | 112,5KVA | ANCORAR | 14.81M | 30K | ANCORAR | (DCIM) | AVENIDA | V4-5 | NVL | 112,5KVA | (DCIM) | P4-30 | NVL | 112,5KVA | AVENIDA | (KL) | 30K | CE4 | BT | 112,5KVA | 80575</t>
+          <t>512716 | 6 | BF-A | 1 | 7 | 2 | EP | 1 | RUA | RUA | 5 | BF-A | (DCIM) | ANCORAR | 4 | (DCIM)</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -661,11 +661,11 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>ANCORAR | CE4112,5KVA | C14X1000112,5KVACE2 | P4-30 | 3x336AN | V6-7 | CE4 | 112,5KVA112,5KVA400816F | LADO | C12x600,B1F,CF-H | MT | BF-A | CF-H | 691498 | 3x185AX(5AZN) | RAMAL | C14X1000112,5KVACE2 | CHAVE | NVL | 112,5KVA112,5KVA | CF-H112,5KVA | LADO | 30K | RUA | V4-5 | FACA | BM | 691498 | 112,5KVA | 32M | C14X1000112,5KVACE4 | C12x600,B1F,CF-H</t>
+          <t>1RU6A | CE4112,5KVA | C14X1000112,5KVACE2 | 3x336AN | CE4 | 2112,5KVA8 | LADO | MT | C12x600,B1F,CF-H | BF-A | CF-H | 3x185AX(5AZN) | 691498 | 1RU6A</t>
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -706,11 +706,11 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33.26M | 33.29M | 30K | BM | 80575 | NF | 175ET005296879 | 3x185AX(5AZN) | (DCIM) | 3x300AX-Q(6AZN) | MT | V3-4 | MT | 534203 | EP | BF-A | 512716 | P31</t>
+          <t>(DCIM) | CF-H | NF | C14X1000112,5KVACE2 | C12x600,B1F,CF-H | CF-H112,5KVA | BM</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>RUA | LADO | CHAVE | FACA | 112,5KVA112,5KVA | 691498 | NVL | BF-A | 691498 | C12x600,B1F,CF-H | CF-H112,5KVA | C14X1000112,5KVACE2 | CF-H | C12x600,B1F,CF-H | RAMAL | 30K</t>
+          <t>C12x600,B1F,CF-H | BF-A | 691498 | NVL | 2112,5KVA | CF-H | LADO | C14X1000112,5KVACE2 | CF-H112,5KVA | RUA | 691498 | CHAVE | 1RU6A | CE4112,5KVA | C12x600,B1F,CF-H | 3x336AN</t>
         </is>
       </c>
       <c r="I6" s="4" t="n">
@@ -800,11 +800,11 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36.36M | 36.55M | 30K | 534203 | AVENIDA | BT | CABOS | AVENIDA | ANCORAR | 3x185AX(5AZN) | ANCORAR | 3x300AX-Q(6AZN) | (DCIM) | 112,5KVA | (KL) | AVENIDA | MT | C12x600,B1F,CF-H | ANCORAR | MT | V2-3 | BT | CABOS | AVENIDA | ESTR. | 32.63M</t>
+          <t>36.36M | 36.55M | 3</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NAO</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>LADO | RUA | 112,5KVA112,5KVA | NVL | CE2112,5KVA | C14X1000112,5KVACE4 | CE2 | P2</t>
+          <t>LADO | RUA | 2112,5KVA | NVL | CE2112,5KVA | C14X1000112,5KVACE4 | CE2</t>
         </is>
       </c>
       <c r="I8" s="4" t="n">
@@ -894,11 +894,11 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32.94M | 32.63M | 30K | ESTR. | 36.36M | 3x185AX(5AZN) | AVENIDA | 3x300AX-Q(6AZN) | CABOS | BT | ANCORAR | AVENIDA | (KL) | MT | 36.55M | MT | V1-2 | 112,5KVA | (DCIM) | 3x300AX-Q(6AZN) | ANCORAR | 112,5KVA | BCU | MT</t>
+          <t>ESTR. | AVENIDA | CABOS | BT | CE4 | 1RU6A | AVENIDA | (KL) | C14X1000112,5KVACE2 | 112,5KVA | (DCIM) | CE4112,5KVA | ANCORAR | CE2112,5KVA</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>P1-11 | 30K | V1-9 | 112,5KVA | 1x2x4AC | V1-9 | CE4112,5KVA | 37,5KVA | 3x336AN | C14X1000112,5KVACE2 | 112,5KVA | 112,5KVA | 112,5KVA | CAMPO | 112,5KVA | 112,5KVA | CE4 | BT | BT | 112,5KVA | NVL | BCU | ANCORAR | AVENIDA | 3x336AN | CLANDESTINOS: | 3x336AN | 112,5KVA | 3x336AN | 3x336AN | 112,5KVA112,5KVA | ANCORAR | (DCIM) | LADO | RUA | ESTR. | AVENIDA | CABOS | BT</t>
+          <t>0 | 9 | 1 | 4 | 9 | CE4112,5KVA | 7 | 6 | C14X1000112,5KVACE2 | 1 | 2 | 112,5KVA | CAMPO | 112,5KVA | 112,5KVA | CE4 | BT | BT | 112,5KVA | NVL | 1RU6A | ANCORAR | AVENIDA | 3x336AN | CLANDESTINOS: | 3x336AN | 112,5KVA | 3x336AN | 3x336AN | 2112,5KVA | ANCORAR | (DCIM) | LADO</t>
         </is>
       </c>
       <c r="I10" s="4" t="n">

--- a/output_excel/16794910.xlsx
+++ b/output_excel/16794910.xlsx
@@ -470,20 +470,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,35 +512,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Rua / Avenida</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ancoragem</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Lado Forte</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Metragem</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Altura Poste</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Informações</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Confiança</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Corrigido IA</t>
         </is>
@@ -562,29 +580,32 @@
           <t>V4-5</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>14.81m</t>
-        </is>
-      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>AV. | LAURO | 2</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
+          <t>32m</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>MT 3x185AX(5AZN) | 32M | 14.81M | CE3112,5KVAM1F112,5KVANVL NVL 1112,5KVA2112,5KVALADO LADO | V4-5 | MT 3x336AN 13.99M</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>NAO</t>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
         </is>
       </c>
     </row>
@@ -610,20 +631,31 @@
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>512716 | 6 | BF-A | 1 | 7 | 2 | EP | 1 | RUA | RUA | 5 | BF-A | (DCIM) | ANCORAR | 4 | (DCIM)</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>14m</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>1 1AF(1)112,5KVA2 CS's 4 3 (DCIM) 4 (DCIM) | C14X1000112,5KVACE2 | EP 15681 2 V1-3 512716 | 2 2X,CE3 | C14X1000112,5KVACE4</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -649,30 +681,33 @@
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>14m</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1RU6A | CE4112,5KVA | C14X1000112,5KVACE2 | 3x336AN | CE4 | 2112,5KVA8 | LADO | MT | C12x600,B1F,CF-H | BF-A | CF-H | 3x185AX(5AZN) | 691498 | 1RU6A</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>C14X1000112,5KVACE2 | C14X1000112,5KVACE2 | C14X1000112,5KVACE4 | 2 2X,CE3 | P4-30 1RU6A CE4112,5KVA1x4ANA V6-7 2112,5KVA8 LADO | CE4 | CF-H C12x600,B1F,CF-H 2 V1-3 691498 | MT 3x185AX(5AZN)</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -697,27 +732,30 @@
           <t>V3-4</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>33.26m</t>
-        </is>
-      </c>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>(DCIM) | CF-H | NF | C14X1000112,5KVACE2 | C12x600,B1F,CF-H | CF-H112,5KVA | BM</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+          <t>33.26m</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>33.26M | 33.29M | xBM | MT 3x185AX(5AZN) | MT 3x300AX-Q(6AZN) | MT 3x185AX(5AZN) | 36.55M | 36.36M</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -743,30 +781,33 @@
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>12m</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>C12x600,B1F,CF-H | BF-A | 691498 | NVL | 2112,5KVA | CF-H | LADO | C14X1000112,5KVACE2 | CF-H112,5KVA | RUA | 691498 | CHAVE | 1RU6A | CE4112,5KVA | C12x600,B1F,CF-H | 3x336AN</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="n">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>14m</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>C14X1000112,5KVACE2 | C14X1000112,5KVACE2 | CF-H C12x600,B1F,CF-H 2 V1-3 691498 | CF-H112,5KVANVL 2112,5KVALADO | C14X1000112,5KVACE4 | P31 C12x600,B1F,CF-H 691498 | P4-30 1RU6A CE4112,5KVA1x4ANA V6-7 2112,5KVA8 LADO</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -791,29 +832,32 @@
           <t>V2-3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>36.36m</t>
-        </is>
-      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36.36M | 36.55M | 3</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
+          <t>36.36m</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>36.36M | 36.55M | MT 3x185AX(5AZN) | MT 3x300AX-Q(6AZN) | 32.63M | 33.26M | 32.94M | MT 3x300AX-Q(6AZN)</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>NAO</t>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
         </is>
       </c>
     </row>
@@ -837,30 +881,33 @@
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>14m</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>LADO | RUA | 2112,5KVA | NVL | CE2112,5KVA | C14X1000112,5KVACE4 | CE2</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="n">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>P2 C14X1000112,5KVACE4 CE2112,5KVANVL 2112,5KVALADO | 1 C14X1000112,5KVACE2 CE4112,5KVANVL 2112,5KVALADO | CE2 | C14X1000112,5KVACE2 | 2 CS's BT AVENIDA</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -885,27 +932,30 @@
           <t>V1-2</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>32.94m</t>
-        </is>
-      </c>
+      <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>ESTR. | AVENIDA | CABOS | BT | CE4 | 1RU6A | AVENIDA | (KL) | C14X1000112,5KVACE2 | 112,5KVA | (DCIM) | CE4112,5KVA | ANCORAR | CE2112,5KVA</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
+          <t>32.94m</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>32.94M | 32.63M | 36.36M | 36.55M | CE4 | MT 3x300AX-Q(6AZN) | MT 3x185AX(5AZN) | MT 3x300AX-Q(6AZN)</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -931,30 +981,33 @@
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>14m</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0 | 9 | 1 | 4 | 9 | CE4112,5KVA | 7 | 6 | C14X1000112,5KVACE2 | 1 | 2 | 112,5KVA | CAMPO | 112,5KVA | 112,5KVA | CE4 | BT | BT | 112,5KVA | NVL | 1RU6A | ANCORAR | AVENIDA | 3x336AN | CLANDESTINOS: | 3x336AN | 112,5KVA | 3x336AN | 3x336AN | 2112,5KVA | ANCORAR | (DCIM) | LADO</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="n">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1 C14X1000112,5KVACE2 CE4112,5KVANVL 2112,5KVALADO | 112,5KVA 2 4 9 0 P1-11 | CLANDESTINOS: 1x4ANA 1RU6A 112,5KVA CAMPO 112,5KVA 1 6 7 9 | P2 C14X1000112,5KVACE4 CE2112,5KVANVL 2112,5KVALADO | CE4</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
